--- a/tabular/reference/repeat/repeat_data.xlsx
+++ b/tabular/reference/repeat/repeat_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/repeat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909949E4-0FEB-F84F-9ECE-9ADB63E0F559}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E0A01-E416-8844-99E3-8EBE8673238E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="1380" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tabular/reference/repeat/repeat_data.xlsx
+++ b/tabular/reference/repeat/repeat_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/repeat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E0A01-E416-8844-99E3-8EBE8673238E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4252F3B-1582-444A-8862-1CF815300CB7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="1380" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10440" yWindow="600" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>

--- a/tabular/reference/repeat/repeat_data.xlsx
+++ b/tabular/reference/repeat/repeat_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/repeat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4252F3B-1582-444A-8862-1CF815300CB7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E9E129-3E05-0347-B667-67D48AE84A91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="600" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="600" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="included" sheetId="2" r:id="rId1"/>

--- a/tabular/reference/repeat/repeat_data.xlsx
+++ b/tabular/reference/repeat/repeat_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/repeat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E9E129-3E05-0347-B667-67D48AE84A91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D316AF-74A3-1945-846D-240C8C21E511}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3300" yWindow="600" windowWidth="25500" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
